--- a/Assessment Questions/CDA/ADA-134/DATA ANALYTICS FOUNDATION/. Business Analytics Overview/. Business Analytics Overview.xlsx
+++ b/Assessment Questions/CDA/ADA-134/DATA ANALYTICS FOUNDATION/. Business Analytics Overview/. Business Analytics Overview.xlsx
@@ -1,147 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\manfo\Downloads\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{54F76AAC-8EB2-45D3-8A8C-640307BE43D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{707B3858-75A8-4099-8D6E-8E702937BB21}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
-  <si>
-    <t>Section,Type,Q.No,Scenario,Question,Option A,Option B,Option C,Option D,Correct Answer</t>
-  </si>
-  <si>
-    <t>SECTION A: Medium Level MCQs,MCQ,1,,What is Business Analytics?,The process of collecting raw data only,The practice of using data and statistical methods to gain insights and support decision-making,Creating charts and graphs for presentations,Storing data in databases,B</t>
-  </si>
-  <si>
-    <t>SECTION A: Medium Level MCQs,MCQ,2,,Which of the following BEST describes the goal of Business Analytics?,To collect as much data as possible,To replace human decision-makers with computers,To transform data into actionable insights for better decisions,To create complex mathematical formulas,C</t>
-  </si>
-  <si>
-    <t>SECTION A: Medium Level MCQs,MCQ,3,,Business Analytics is different from Business Intelligence because:,BI focuses on past; BA focuses on future predictions and optimization,They are exactly the same,BA focuses only on reporting,BI uses only AI,A</t>
-  </si>
-  <si>
-    <t>SECTION A: Medium Level MCQs,MCQ,4,,The DIKW pyramid in analytics represents:,Data, Information, Knowledge, Wisdom,Direct, Indirect, Knowledge, Work,Data, Index, Key, Word,Digital, Internet, Knowledge, Web,A</t>
-  </si>
-  <si>
-    <t>SECTION A: Medium Level MCQs,MCQ,5,,Which of the following is NOT a typical component of Business Analytics?,Data collection and preparation,Statistical analysis and modeling,Random guessing,Data visualization,C</t>
-  </si>
-  <si>
-    <t>SECTION A: Medium Level MCQs,MCQ,6,,The term ""Data-Driven Decision Making"" means:,Making decisions based on intuition only,Making decisions based on data and evidence,Making decisions randomly,Avoiding decisions altogether,B</t>
-  </si>
-  <si>
-    <t>SECTION A: Medium Level MCQs,MCQ,7,,Which statement about Business Analytics is TRUE?,It guarantees 100% accurate predictions,It only works for large companies,It helps reduce uncertainty in decision-making,It eliminates the need for human judgment,C</t>
-  </si>
-  <si>
-    <t>SECTION B: Scenario-Based Questions,Scenario,8,A retail manager looks at last month's sales report to decide which products to reorder.,This is an example of using analytics for:,Descriptive purposes only,Predictive modeling,Prescriptive optimization,Data collection,A</t>
-  </si>
-  <si>
-    <t>SECTION B: Scenario-Based Questions,Scenario,9,A bank uses historical data to predict which customers might default on loans.,This is an example of:,Descriptive Analytics,Diagnostic Analytics,Predictive Analytics,Prescriptive Analytics,C</t>
-  </si>
-  <si>
-    <t>SECTION B: Scenario-Based Questions,Scenario,10,An e-commerce company uses customer browsing data to recommend products.,This application of analytics helps with:,Increasing operational costs,Personalizing customer experience,Reducing product quality,Eliminating customer service,B</t>
-  </si>
-  <si>
-    <t>SECTION B: Scenario-Based Questions,Scenario,11,A hospital uses analytics to predict patient readmission rates.,This helps them:,Increase readmissions,Identify high-risk patients for follow-up care,Reduce staff salaries,Eliminate patient records,B</t>
-  </si>
-  <si>
-    <t>SECTION B: Scenario-Based Questions,Scenario,12,A logistics company uses analytics to optimize delivery routes.,This application helps with:,Increasing fuel consumption,Reducing delivery time and costs,Hiring more drivers,Slowing down deliveries,B</t>
-  </si>
-  <si>
-    <t>SECTION C: Dataset,Dataset,Week,,Sales ($),Customers,Marketing Spend ($),Competitor Price ($),</t>
-  </si>
-  <si>
-    <t>SECTION C: Dataset,Dataset,1,,5000,250,200,25,</t>
-  </si>
-  <si>
-    <t>SECTION C: Dataset,Dataset,2,,5200,260,220,25,</t>
-  </si>
-  <si>
-    <t>SECTION C: Dataset,Dataset,3,,5500,275,250,24,</t>
-  </si>
-  <si>
-    <t>SECTION C: Dataset,Dataset,4,,5800,290,280,24,</t>
-  </si>
-  <si>
-    <t>SECTION C: Dataset,Dataset,5,,6200,310,320,23,</t>
-  </si>
-  <si>
-    <t>SECTION C: Dataset,Dataset,6,,6500,325,350,23,</t>
-  </si>
-  <si>
-    <t>SECTION C: Dataset,Dataset,7,,6800,340,380,22,</t>
-  </si>
-  <si>
-    <t>SECTION C: Dataset,Dataset,8,,7200,360,420,22,</t>
-  </si>
-  <si>
-    <t>SECTION C: Practical Questions,Practical,13,,Calculate the average weekly sales for the 8-week period. Show your formula and answer.,,,,,</t>
-  </si>
-  <si>
-    <t>SECTION C: Practical Questions,Practical,14,,Calculate the percentage growth in sales from Week 1 to Week 8. Show your calculation.,,,,,</t>
-  </si>
-  <si>
-    <t>SECTION C: Practical Questions,Practical,15,,Create a simple line chart description showing sales trend over the 8 weeks. Is the trend increasing, decreasing, or flat?,,,,,</t>
-  </si>
-  <si>
-    <t>SECTION C: Practical Questions,Practical,16,,Calculate the correlation between Marketing Spend and Sales. What does this tell you about the relationship?,,,,,</t>
-  </si>
-  <si>
-    <t>SECTION C: Practical Questions,Practical,17,,If the store wants to predict sales for Week 9 based on the trend, what would be a reasonable estimate? Show your reasoning.,,,,,</t>
-  </si>
-  <si>
-    <t>SECTION C: Practical Questions,Practical,18,,Calculate the average sales per customer (Sales ÷ Customers) for each week. Which week had the highest average transaction value?,,,,,</t>
-  </si>
-  <si>
-    <t>SECTION C: Practical Questions,Practical,19,,Compare Week 3 and Week 6. By what percentage did sales increase? By what percentage did marketing spend increase?,,,,,</t>
-  </si>
-  <si>
-    <t>SECTION C: Practical Questions,Practical,20,,Based on this data, what two recommendations would you give to the store manager to improve business performance?,,,,,</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -160,21 +46,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -474,158 +419,1049 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99292706-C5E2-434A-A996-284A16CEAFC8}">
-  <dimension ref="A1:A33"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J30"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Question No.</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Topic</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Question Type</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Question</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Scenario/Context</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Skills Tested</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Option A</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Option B</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Option C</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Option D</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>. Business Analytics Overview</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>MCQ</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>What is Business Analytics?</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>SECTION A: Medium Level MCQs</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>The process of collecting raw data only</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>The practice of using data and statistical methods to gain insights and support decision-making</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Creating charts and graphs for presentations</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Storing data in databases</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>. Business Analytics Overview</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>MCQ</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Which of the following BEST describes the goal of Business Analytics?</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>SECTION A: Medium Level MCQs</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>To collect as much data as possible</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>To replace human decision-makers with computers</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>To transform data into actionable insights for better decisions</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>To create complex mathematical formulas</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
         <v>3</v>
       </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>. Business Analytics Overview</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>MCQ</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Business Analytics is different from Business Intelligence because:</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>SECTION A: Medium Level MCQs</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>BI focuses on past; BA focuses on future predictions and optimization</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>They are exactly the same</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>BA focuses only on reporting</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>BI uses only AI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
         <v>4</v>
       </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>. Business Analytics Overview</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>MCQ</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>The DIKW pyramid in analytics represents:</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>SECTION A: Medium Level MCQs</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Data, Information, Knowledge, Wisdom</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Direct, Indirect, Knowledge, Work</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Data, Index, Key, Word</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Digital, Internet, Knowledge, Web</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
         <v>5</v>
       </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>. Business Analytics Overview</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>MCQ</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Which of the following is NOT a typical component of Business Analytics?</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>SECTION A: Medium Level MCQs</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Data collection and preparation</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Statistical analysis and modeling</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Random guessing</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Data visualization</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
         <v>6</v>
       </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>. Business Analytics Overview</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>MCQ</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>The term ""Data-Driven Decision Making"" means:</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>SECTION A: Medium Level MCQs</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Making decisions based on intuition only</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Making decisions based on data and evidence</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Making decisions randomly</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Avoiding decisions altogether</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
         <v>7</v>
       </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>. Business Analytics Overview</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>MCQ</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Which statement about Business Analytics is TRUE?</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>SECTION A: Medium Level MCQs</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>It guarantees 100% accurate predictions</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>It only works for large companies</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>It helps reduce uncertainty in decision-making</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>It eliminates the need for human judgment</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
         <v>8</v>
       </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>. Business Analytics Overview</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Scenario-Based</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>This is an example of using analytics for:</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>SECTION B: Scenario-Based Questions | A retail manager looks at last month's sales report to decide which products to reorder.</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Descriptive purposes only</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Predictive modeling</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Prescriptive optimization</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Data collection</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
         <v>9</v>
       </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>. Business Analytics Overview</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Scenario-Based</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>This is an example of:</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>SECTION B: Scenario-Based Questions | A bank uses historical data to predict which customers might default on loans.</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Descriptive Analytics</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Diagnostic Analytics</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Predictive Analytics</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Prescriptive Analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
         <v>10</v>
       </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>. Business Analytics Overview</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Scenario-Based</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>This application of analytics helps with:</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>SECTION B: Scenario-Based Questions | An e-commerce company uses customer browsing data to recommend products.</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Increasing operational costs</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Personalizing customer experience</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Reducing product quality</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Eliminating customer service</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
         <v>11</v>
       </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>. Business Analytics Overview</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Scenario-Based</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>This helps them:</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>SECTION B: Scenario-Based Questions | A hospital uses analytics to predict patient readmission rates.</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Increase readmissions</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Identify high-risk patients for follow-up care</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Reduce staff salaries</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Eliminate patient records</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
         <v>12</v>
       </c>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>. Business Analytics Overview</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Scenario-Based</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>This application helps with:</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>SECTION B: Scenario-Based Questions | A logistics company uses analytics to optimize delivery routes.</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Increasing fuel consumption</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Reducing delivery time and costs</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Hiring more drivers</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Slowing down deliveries</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
         <v>13</v>
       </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>. Business Analytics Overview</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dataset row - Source: Week | Spend ($): Sales ($) | Impressions: Customers | Clicks: Marketing Spend ($) | Conversions: Competitor Price ($) | Revenue ($): </t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>SECTION C: Dataset</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
         <v>14</v>
       </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>. Business Analytics Overview</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dataset row - Source: 1 | Spend ($): 5000 | Impressions: 250 | Clicks: 200 | Conversions: 25 | Revenue ($): </t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>SECTION C: Dataset</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
         <v>15</v>
       </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>. Business Analytics Overview</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dataset row - Source: 2 | Spend ($): 5200 | Impressions: 260 | Clicks: 220 | Conversions: 25 | Revenue ($): </t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>SECTION C: Dataset</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
         <v>16</v>
       </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>. Business Analytics Overview</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dataset row - Source: 3 | Spend ($): 5500 | Impressions: 275 | Clicks: 250 | Conversions: 24 | Revenue ($): </t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>SECTION C: Dataset</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
         <v>17</v>
       </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>. Business Analytics Overview</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dataset row - Source: 4 | Spend ($): 5800 | Impressions: 290 | Clicks: 280 | Conversions: 24 | Revenue ($): </t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>SECTION C: Dataset</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
         <v>18</v>
       </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>. Business Analytics Overview</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dataset row - Source: 5 | Spend ($): 6200 | Impressions: 310 | Clicks: 320 | Conversions: 23 | Revenue ($): </t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>SECTION C: Dataset</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
         <v>19</v>
       </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>. Business Analytics Overview</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dataset row - Source: 6 | Spend ($): 6500 | Impressions: 325 | Clicks: 350 | Conversions: 23 | Revenue ($): </t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>SECTION C: Dataset</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
         <v>20</v>
       </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>. Business Analytics Overview</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dataset row - Source: 7 | Spend ($): 6800 | Impressions: 340 | Clicks: 380 | Conversions: 22 | Revenue ($): </t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>SECTION C: Dataset</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
         <v>21</v>
       </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>. Business Analytics Overview</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dataset row - Source: 8 | Spend ($): 7200 | Impressions: 360 | Clicks: 420 | Conversions: 22 | Revenue ($): </t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>SECTION C: Dataset</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
         <v>22</v>
       </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>. Business Analytics Overview</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Calculate the average weekly sales for the 8-week period. Show your formula and answer.</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>SECTION C: Practical Questions</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
         <v>23</v>
       </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>. Business Analytics Overview</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Calculate the percentage growth in sales from Week 1 to Week 8. Show your calculation.</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>SECTION C: Practical Questions</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
         <v>24</v>
       </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>. Business Analytics Overview</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Create a simple line chart description showing sales trend over the 8 weeks. Is the trend increasing</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>SECTION C: Practical Questions</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>decreasing</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>or flat?</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
         <v>25</v>
       </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>. Business Analytics Overview</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Calculate the correlation between Marketing Spend and Sales. What does this tell you about the relationship?</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>SECTION C: Practical Questions</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
         <v>26</v>
       </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>. Business Analytics Overview</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>If the store wants to predict sales for Week 9 based on the trend</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>SECTION C: Practical Questions</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>what would be a reasonable estimate? Show your reasoning.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
         <v>27</v>
       </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>. Business Analytics Overview</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Calculate the average sales per customer (Sales ÷ Customers) for each week. Which week had the highest average transaction value?</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>SECTION C: Practical Questions</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
         <v>28</v>
       </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>. Business Analytics Overview</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Compare Week 3 and Week 6. By what percentage did sales increase? By what percentage did marketing spend increase?</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>SECTION C: Practical Questions</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
         <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>. Business Analytics Overview</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Based on this data</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>SECTION C: Practical Questions</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>what two recommendations would you give to the store manager to improve business performance?</t>
+        </is>
       </c>
     </row>
   </sheetData>
